--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DataAnalytics\Excel_Data_Analytics\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DACF0C-E6D1-403B-A48D-03B483E33508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92700DC8-3AB6-46A6-B6ED-DA01E5E1C716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-102" yWindow="1488" windowWidth="18372" windowHeight="10296" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>
@@ -36,8 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -45,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -866,7 +864,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -950,7 +948,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -962,7 +959,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1320,32 +1317,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D423364-12D3-4C3A-8A6B-C3645EBFE927}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.15625" style="1"/>
-    <col min="18" max="18" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.109375" style="1"/>
+    <col min="18" max="18" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1395,7 +1392,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1452,9 +1449,12 @@
         <f>AND(L3,M3)</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="32"/>
-    </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q3" s="32" t="str">
+        <f>IF(P3,"Goal Met","Not Met")</f>
+        <v>Goal Met</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1511,9 +1511,12 @@
         <f t="shared" ref="P4:P12" si="10">AND(L4,M4)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="32"/>
-    </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q4" s="32" t="str">
+        <f t="shared" ref="Q4:Q12" si="11">IF(P4,"Goal Met","Not Met")</f>
+        <v>Not Met</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1570,9 +1573,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="32"/>
-    </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q5" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Not Met</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1629,9 +1635,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="32"/>
-    </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q6" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Goal Met</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1688,9 +1697,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="32"/>
-    </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q7" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Not Met</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1747,9 +1759,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="32"/>
-    </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q8" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Goal Met</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1806,9 +1821,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="32"/>
-    </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q9" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Goal Met</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1865,9 +1883,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q10" s="32"/>
-    </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q10" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Goal Met</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1924,9 +1945,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="32"/>
-    </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q11" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Not Met</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -1983,14 +2007,17 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q12" s="33"/>
-    </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q12" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>Goal Met</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1998,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2014,33 +2041,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C913A13C-1EE0-4C25-B641-D7D4D62C7E1E}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.41796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.15625" style="1"/>
-    <col min="19" max="19" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="9.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.109375" style="1"/>
+    <col min="19" max="19" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2090,7 +2117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2152,7 +2179,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2214,7 +2241,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -2276,7 +2303,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2365,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -2400,7 +2427,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -2462,7 +2489,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2551,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -2586,7 +2613,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2648,7 +2675,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -2710,12 +2737,12 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -2723,7 +2750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2739,29 +2766,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18E6D21-2229-4383-8B9A-431F68FAE08C}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.15625" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.9453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5234375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.3125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="68.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.21875" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -2817,11 +2844,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="47">
+      <c r="B2" s="46">
         <v>44996.547291666669</v>
       </c>
       <c r="C2" s="27" t="s">
@@ -2848,12 +2875,24 @@
       <c r="J2" s="27" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K2" t="str">
+        <f>IF($A2=K$1,"Role Desired","Not Desired")</f>
+        <v>Not Desired</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF($A2=L$1,"Role Desired","Not Desired")</f>
+        <v>Not Desired</v>
+      </c>
+      <c r="M2" t="str">
+        <f>IF($A2=K$1,"Role Desired",IF($A2=L$1,"Role Desired","Not Desired"))</f>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="46">
         <v>45097.915243055562</v>
       </c>
       <c r="C3" s="27" t="s">
@@ -2880,12 +2919,24 @@
       <c r="J3" s="27" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:L21" si="0">IF($A3=K$1,"Role Desired","Not Desired")</f>
+        <v>Role Desired</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M21" si="1">IF($A3=K$1,"Role Desired",IF($A3=L$1,"Role Desired","Not Desired"))</f>
+        <v>Role Desired</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="46">
         <v>45173.250416666669</v>
       </c>
       <c r="C4" s="27" t="s">
@@ -2910,12 +2961,24 @@
       <c r="J4" s="27" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K4" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desired</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="46">
         <v>45156.253321759257</v>
       </c>
       <c r="C5" s="27" t="s">
@@ -2940,12 +3003,24 @@
       <c r="J5" s="27" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K5" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="46">
         <v>45147.802951388891</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -2970,12 +3045,24 @@
       <c r="J6" s="27" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K6" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="46">
         <v>45202.753101851849</v>
       </c>
       <c r="C7" s="27" t="s">
@@ -3000,12 +3087,24 @@
       <c r="J7" s="27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="46">
         <v>44949.850462962961</v>
       </c>
       <c r="C8" s="27" t="s">
@@ -3030,12 +3129,24 @@
       <c r="J8" s="27" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K8" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desired</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="46">
         <v>45001.627175925933</v>
       </c>
       <c r="C9" s="27" t="s">
@@ -3062,12 +3173,24 @@
       <c r="J9" s="27" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desired</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="46">
         <v>45041.375868055547</v>
       </c>
       <c r="C10" s="27" t="s">
@@ -3092,12 +3215,24 @@
       <c r="J10" s="27" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K10" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desired</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="46">
         <v>45106.587094907409</v>
       </c>
       <c r="C11" s="27" t="s">
@@ -3124,12 +3259,24 @@
       <c r="J11" s="27" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K11" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desired</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>45029.919687499998</v>
       </c>
       <c r="C12" s="27" t="s">
@@ -3156,12 +3303,24 @@
       <c r="J12" s="27" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K12" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="46">
         <v>45091.502789351849</v>
       </c>
       <c r="C13" s="27" t="s">
@@ -3188,12 +3347,24 @@
       <c r="J13" s="27" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K13" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="46">
         <v>45175.543124999997</v>
       </c>
       <c r="C14" s="27" t="s">
@@ -3220,12 +3391,24 @@
       <c r="J14" s="27" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K14" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="46">
         <v>45117.778391203698</v>
       </c>
       <c r="C15" s="27" t="s">
@@ -3252,12 +3435,24 @@
       <c r="J15" s="27" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K15" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="46">
         <v>44938.614351851851</v>
       </c>
       <c r="C16" s="27" t="s">
@@ -3284,12 +3479,24 @@
       <c r="J16" s="27" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K16" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="46">
         <v>44985.354097222233</v>
       </c>
       <c r="C17" s="27" t="s">
@@ -3316,12 +3523,24 @@
       <c r="J17" s="27" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K17" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="47">
+      <c r="B18" s="46">
         <v>45063.792291666658</v>
       </c>
       <c r="C18" s="27" t="s">
@@ -3346,12 +3565,24 @@
       <c r="J18" s="27" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K18" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desired</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="47">
+      <c r="B19" s="46">
         <v>45017.004837962973</v>
       </c>
       <c r="C19" s="27" t="s">
@@ -3378,12 +3609,24 @@
       <c r="J19" s="27" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K19" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="47">
+      <c r="B20" s="46">
         <v>45169.64203703704</v>
       </c>
       <c r="C20" s="27" t="s">
@@ -3408,12 +3651,24 @@
       <c r="J20" s="27" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K20" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21" s="46">
         <v>45000.542685185188</v>
       </c>
       <c r="C21" s="27" t="s">
@@ -3439,6 +3694,18 @@
       </c>
       <c r="J21" s="27" t="s">
         <v>135</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desired</v>
       </c>
     </row>
   </sheetData>
@@ -3449,29 +3716,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4064259-8981-41EE-A951-64D7FCDC9F77}">
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.83984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.15625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.26171875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.41796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -3496,7 +3763,7 @@
       <c r="H1" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="45" t="s">
         <v>54</v>
       </c>
       <c r="J1" s="34" t="s">
@@ -3531,11 +3798,11 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="47">
+      <c r="B2" s="46">
         <v>44996.547291666669</v>
       </c>
       <c r="C2" s="27" t="s">
@@ -3595,11 +3862,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="46">
         <v>45097.915243055562</v>
       </c>
       <c r="C3" s="27" t="s">
@@ -3659,11 +3926,11 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="46">
         <v>45173.250416666669</v>
       </c>
       <c r="C4" s="27" t="s">
@@ -3721,11 +3988,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="46">
         <v>45156.253321759257</v>
       </c>
       <c r="C5" s="27" t="s">
@@ -3783,11 +4050,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="46">
         <v>45147.802951388891</v>
       </c>
       <c r="C6" s="27" t="s">
@@ -3845,11 +4112,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="46">
         <v>45202.753101851849</v>
       </c>
       <c r="C7" s="27" t="s">
@@ -3907,11 +4174,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="46">
         <v>44949.850462962961</v>
       </c>
       <c r="C8" s="27" t="s">
@@ -3969,11 +4236,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="46">
         <v>45001.627175925933</v>
       </c>
       <c r="C9" s="27" t="s">
@@ -4033,11 +4300,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="46">
         <v>45041.375868055547</v>
       </c>
       <c r="C10" s="27" t="s">
@@ -4095,11 +4362,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="46">
         <v>45106.587094907409</v>
       </c>
       <c r="C11" s="27" t="s">
@@ -4159,11 +4426,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>45029.919687499998</v>
       </c>
       <c r="C12" s="27" t="s">
@@ -4223,11 +4490,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="46">
         <v>45091.502789351849</v>
       </c>
       <c r="C13" s="27" t="s">
@@ -4287,11 +4554,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="46">
         <v>45175.543124999997</v>
       </c>
       <c r="C14" s="27" t="s">
@@ -4351,11 +4618,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="46">
         <v>45117.778391203698</v>
       </c>
       <c r="C15" s="27" t="s">
@@ -4415,11 +4682,11 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="46">
         <v>44938.614351851851</v>
       </c>
       <c r="C16" s="27" t="s">
@@ -4479,11 +4746,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="46">
         <v>44985.354097222233</v>
       </c>
       <c r="C17" s="27" t="s">
@@ -4543,11 +4810,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="47">
+      <c r="B18" s="46">
         <v>45063.792291666658</v>
       </c>
       <c r="C18" s="27" t="s">
@@ -4605,11 +4872,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="47">
+      <c r="B19" s="46">
         <v>45017.004837962973</v>
       </c>
       <c r="C19" s="27" t="s">
@@ -4669,11 +4936,11 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="47">
+      <c r="B20" s="46">
         <v>45169.64203703704</v>
       </c>
       <c r="C20" s="27" t="s">
@@ -4731,11 +4998,11 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21" s="46">
         <v>45000.542685185188</v>
       </c>
       <c r="C21" s="27" t="s">
@@ -4804,17 +5071,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EBE098-CD97-45AE-AE7E-86DF2D94E426}">
   <dimension ref="B2:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.578125" customWidth="1"/>
-    <col min="2" max="2" width="13.41796875" customWidth="1"/>
-    <col min="3" max="3" width="31.41796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.41796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
         <v>28</v>
       </c>
@@ -4824,14 +5091,14 @@
       <c r="D2" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="44" t="s">
+      <c r="F2" s="43" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
@@ -4851,7 +5118,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="27" t="e">
         <f>A4 + "text"</f>
         <v>#VALUE!</v>
@@ -4871,7 +5138,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -4891,7 +5158,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="e" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">COUNTT(A3:A9)</f>
         <v>#NAME?</v>
@@ -4911,7 +5178,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="27" t="e">
         <f>VLOOKUP("Value", A1:A10, 2, FALSE)</f>
         <v>#N/A</v>
@@ -4931,7 +5198,7 @@
         <v>This hides #N/A error</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="27" t="e">
         <f>SQRT(-1)</f>
         <v>#NUM!</v>
@@ -4951,7 +5218,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="e">
         <f>SUM(A1:A10 C1:C10)</f>
         <v>#NULL!</v>
@@ -4979,28 +5246,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B83CC08-3BAC-45FD-A105-07186D54808A}">
   <dimension ref="B1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.578125" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="36" t="s">
         <v>137</v>
       </c>
       <c r="C2" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="44" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="38" t="b">
         <v>1</v>
       </c>
@@ -5016,7 +5283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="38" t="b">
         <v>1</v>
       </c>
@@ -5032,7 +5299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="38" t="b">
         <v>0</v>
       </c>
@@ -5048,18 +5315,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="b">
         <v>0</v>
       </c>
       <c r="C6" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="D6" s="43" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E6" s="43" t="b">
+      <c r="D6" s="42" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="42" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>

--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DataAnalytics\Excel_Data_Analytics\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92700DC8-3AB6-46A6-B6ED-DA01E5E1C716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32D91ADC-AFF3-4CDB-B211-05C0A7A062A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Final_2!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2782,10 +2783,9 @@
     <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -2887,6 +2887,26 @@
         <f>IF($A2=K$1,"Role Desired",IF($A2=L$1,"Role Desired","Not Desired"))</f>
         <v>Not Desired</v>
       </c>
+      <c r="N2" t="b">
+        <f>AND($A2=$K$1,$A2=$L$1)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <f>OR($A2=$K$1,$A2=$L$1)</f>
+        <v>0</v>
+      </c>
+      <c r="P2" t="str">
+        <f>IF(OR($A2=$K$1,$A2=$L$1),"Role Desired", "Not Desired")</f>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>IF($H2&gt;$Q$1,"Salaray&gt;85K","Salary Low")</f>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R2" t="str" cm="1">
+        <f t="array" ref="R2">_xlfn.IFS($H2="","No Data",$H2&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
@@ -2931,6 +2951,26 @@
         <f t="shared" ref="M3:M21" si="1">IF($A3=K$1,"Role Desired",IF($A3=L$1,"Role Desired","Not Desired"))</f>
         <v>Role Desired</v>
       </c>
+      <c r="N3" t="b">
+        <f t="shared" ref="N3:N21" si="2">AND($A3=$K$1,$A3=$L$1)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <f t="shared" ref="O3:O21" si="3">OR($A3=$K$1,$A3=$L$1)</f>
+        <v>1</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3:P21" si="4">IF(OR($A3=$K$1,$A3=$L$1),"Role Desired", "Not Desired")</f>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q21" si="5">IF($H3&gt;$Q$1,"Salaray&gt;85K","Salary Low")</f>
+        <v>Salary Low</v>
+      </c>
+      <c r="R3" t="str" cm="1">
+        <f t="array" ref="R3">_xlfn.IFS($H3="","No Data",$H3&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary Low</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
@@ -2973,6 +3013,26 @@
         <f t="shared" si="1"/>
         <v>Role Desired</v>
       </c>
+      <c r="N4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q4" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R4" t="str" cm="1">
+        <f t="array" ref="R4">_xlfn.IFS($H4="","No Data",$H4&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
@@ -3015,6 +3075,26 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
+      <c r="N5" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R5" t="str" cm="1">
+        <f t="array" ref="R5">_xlfn.IFS($H5="","No Data",$H5&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
@@ -3057,6 +3137,26 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
+      <c r="N6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R6" t="str" cm="1">
+        <f t="array" ref="R6">_xlfn.IFS($H6="","No Data",$H6&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
@@ -3099,6 +3199,26 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
+      <c r="N7" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R7" t="str" cm="1">
+        <f t="array" ref="R7">_xlfn.IFS($H7="","No Data",$H7&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
@@ -3141,6 +3261,26 @@
         <f t="shared" si="1"/>
         <v>Role Desired</v>
       </c>
+      <c r="N8" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R8" t="str" cm="1">
+        <f t="array" ref="R8">_xlfn.IFS($H8="","No Data",$H8&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
@@ -3185,6 +3325,26 @@
         <f t="shared" si="1"/>
         <v>Role Desired</v>
       </c>
+      <c r="N9" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R9" t="str" cm="1">
+        <f t="array" ref="R9">_xlfn.IFS($H9="","No Data",$H9&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
@@ -3227,6 +3387,26 @@
         <f t="shared" si="1"/>
         <v>Role Desired</v>
       </c>
+      <c r="N10" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R10" t="str" cm="1">
+        <f t="array" ref="R10">_xlfn.IFS($H10="","No Data",$H10&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
@@ -3271,6 +3451,26 @@
         <f t="shared" si="1"/>
         <v>Role Desired</v>
       </c>
+      <c r="N11" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R11" t="str" cm="1">
+        <f t="array" ref="R11">_xlfn.IFS($H11="","No Data",$H11&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
@@ -3315,6 +3515,26 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
+      <c r="N12" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R12" t="str" cm="1">
+        <f t="array" ref="R12">_xlfn.IFS($H12="","No Data",$H12&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
@@ -3359,6 +3579,26 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
+      <c r="N13" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R13" t="str" cm="1">
+        <f t="array" ref="R13">_xlfn.IFS($H13="","No Data",$H13&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
@@ -3403,6 +3643,26 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
+      <c r="N14" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R14" t="str" cm="1">
+        <f t="array" ref="R14">_xlfn.IFS($H14="","No Data",$H14&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
@@ -3447,6 +3707,26 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
+      <c r="N15" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R15" t="str" cm="1">
+        <f t="array" ref="R15">_xlfn.IFS($H15="","No Data",$H15&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary Low</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
@@ -3491,8 +3771,28 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N16" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R16" t="str" cm="1">
+        <f t="array" ref="R16">_xlfn.IFS($H16="","No Data",$H16&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
@@ -3535,8 +3835,28 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N17" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R17" t="str" cm="1">
+        <f t="array" ref="R17">_xlfn.IFS($H17="","No Data",$H17&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
@@ -3577,8 +3897,28 @@
         <f t="shared" si="1"/>
         <v>Role Desired</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N18" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R18" t="str" cm="1">
+        <f t="array" ref="R18">_xlfn.IFS($H18="","No Data",$H18&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
@@ -3621,8 +3961,28 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N19" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q19" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R19" t="str" cm="1">
+        <f t="array" ref="R19">_xlfn.IFS($H19="","No Data",$H19&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -3663,8 +4023,28 @@
         <f t="shared" si="1"/>
         <v>Not Desired</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N20" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" t="str">
+        <f t="shared" si="4"/>
+        <v>Not Desired</v>
+      </c>
+      <c r="Q20" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R20" t="str" cm="1">
+        <f t="array" ref="R20">_xlfn.IFS($H20="","No Data",$H20&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
@@ -3706,6 +4086,26 @@
       <c r="M21" t="str">
         <f t="shared" si="1"/>
         <v>Role Desired</v>
+      </c>
+      <c r="N21" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O21" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q21" t="str">
+        <f t="shared" si="5"/>
+        <v>Salaray&gt;85K</v>
+      </c>
+      <c r="R21" t="str" cm="1">
+        <f t="array" ref="R21">_xlfn.IFS($H21="","No Data",$H21&gt;=$Q$1,"Salary&gt;$85K",TRUE,"Salary Low")</f>
+        <v>Salary&gt;$85K</v>
       </c>
     </row>
   </sheetData>
@@ -5291,11 +5691,11 @@
         <v>0</v>
       </c>
       <c r="D4" s="42" t="b">
-        <f t="shared" ref="D4:D6" si="0">AND(B4,C4)</f>
+        <f>AND(B4,C4)</f>
         <v>0</v>
       </c>
       <c r="E4" s="42" t="b">
-        <f t="shared" ref="E4:E6" si="1">OR(B4,C4)</f>
+        <f>OR(B4,C4)</f>
         <v>1</v>
       </c>
     </row>
@@ -5307,11 +5707,11 @@
         <v>1</v>
       </c>
       <c r="D5" s="42" t="b">
-        <f t="shared" si="0"/>
+        <f>AND(B5,C5)</f>
         <v>0</v>
       </c>
       <c r="E5" s="42" t="b">
-        <f t="shared" si="1"/>
+        <f>OR(B5,C5)</f>
         <v>1</v>
       </c>
     </row>
@@ -5323,11 +5723,11 @@
         <v>0</v>
       </c>
       <c r="D6" s="42" t="b">
-        <f t="shared" si="0"/>
+        <f>AND(B6,C6)</f>
         <v>0</v>
       </c>
       <c r="E6" s="42" t="b">
-        <f t="shared" si="1"/>
+        <f>OR(B6,C6)</f>
         <v>0</v>
       </c>
     </row>

--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DataAnalytics\Excel_Data_Analytics\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32D91ADC-AFF3-4CDB-B211-05C0A7A062A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE421459-834F-4A32-875B-9D83AE139A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Final_2!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1325,15 +1324,15 @@
     <col min="3" max="3" width="18.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.109375" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.21875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.21875" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="1" customWidth="1"/>
+    <col min="8" max="9" width="11.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.21875" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.21875" style="1" customWidth="1"/>
     <col min="13" max="13" width="9.109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.44140625" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" style="1" customWidth="1"/>
     <col min="16" max="16" width="9.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="9.109375" style="1"/>
     <col min="18" max="18" width="14.109375" style="1" bestFit="1" customWidth="1"/>
